--- a/tables/new/balanced all/all_ap.xlsx
+++ b/tables/new/balanced all/all_ap.xlsx
@@ -425,36 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
+          <t>Logit(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 1, 1)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>XGBoost(1, 1, 1, 1)</t>
         </is>
@@ -467,21 +457,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5800541038194007</v>
+        <v>0.6416373995565015</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6416373995565015</v>
+        <v>0.609284269811423</v>
       </c>
       <c r="D2" t="n">
-        <v>0.609284269811423</v>
+        <v>0.6377473734707846</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6377473734707846</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5968356644917263</v>
-      </c>
-      <c r="G2" t="n">
         <v>0.6354263812856096</v>
       </c>
     </row>
@@ -492,21 +476,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4748360713552803</v>
+        <v>0.4914295998853091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4914295998853091</v>
+        <v>0.4892969355276154</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4892969355276154</v>
+        <v>0.4433489364989719</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4433489364989719</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.4906617878806166</v>
-      </c>
-      <c r="G3" t="n">
         <v>0.4508855630411611</v>
       </c>
     </row>
@@ -517,21 +495,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9937853083038756</v>
+        <v>0.9866998972489356</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9866998972489356</v>
+        <v>0.9910151022796582</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9910151022796582</v>
+        <v>0.9885898821598108</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9885898821598108</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9932215156243808</v>
-      </c>
-      <c r="G4" t="n">
         <v>0.99125037972145</v>
       </c>
     </row>
@@ -542,21 +514,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4346970701823003</v>
+        <v>0.4763775555395118</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4763775555395118</v>
+        <v>0.4339902559540924</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4339902559540924</v>
+        <v>0.4665260854039462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4665260854039462</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.4234717277789636</v>
-      </c>
-      <c r="G5" t="n">
         <v>0.4689349940489087</v>
       </c>
     </row>
@@ -567,21 +533,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9045614295826984</v>
+        <v>0.9235634408798232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9235634408798232</v>
+        <v>0.9140737090640833</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9140737090640833</v>
+        <v>0.9207259977325708</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9207259977325708</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9080618873564824</v>
-      </c>
-      <c r="G6" t="n">
         <v>0.9164303208257368</v>
       </c>
     </row>
@@ -592,21 +552,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7986155936212495</v>
+        <v>0.8520471379468122</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8520471379468122</v>
+        <v>0.7981999081682284</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7981999081682284</v>
+        <v>0.8505462537055943</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8505462537055943</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8053775429722082</v>
-      </c>
-      <c r="G7" t="n">
         <v>0.8631799545679144</v>
       </c>
     </row>
@@ -617,21 +571,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5800080324386745</v>
+        <v>0.5960753164310284</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5960753164310284</v>
+        <v>0.5852659576333044</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5852659576333044</v>
+        <v>0.5914430360591405</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5914430360591405</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.5855424939918916</v>
-      </c>
-      <c r="G8" t="n">
         <v>0.6067379847821912</v>
       </c>
     </row>
@@ -642,21 +590,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8888518842692207</v>
+        <v>0.8937826381243928</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8937826381243928</v>
+        <v>0.8620559897945409</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8620559897945409</v>
+        <v>0.8606852279880461</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8606852279880461</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8745368596998125</v>
-      </c>
-      <c r="G9" t="n">
         <v>0.8901922609972572</v>
       </c>
     </row>
@@ -667,21 +609,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4788281038750628</v>
+        <v>0.5258158768428689</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5258158768428689</v>
+        <v>0.495150611091595</v>
       </c>
       <c r="D10" t="n">
-        <v>0.495150611091595</v>
+        <v>0.4828184609791839</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4828184609791839</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.4919973386447921</v>
-      </c>
-      <c r="G10" t="n">
         <v>0.520811000095816</v>
       </c>
     </row>
@@ -692,21 +628,15 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8709381847072278</v>
+        <v>0.9714648238875996</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9714648238875996</v>
+        <v>0.8738070535380673</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8738070535380673</v>
+        <v>0.9616088395243274</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9616088395243274</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.8716155949813862</v>
-      </c>
-      <c r="G11" t="n">
         <v>0.9633202985529732</v>
       </c>
     </row>
@@ -717,21 +647,15 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4890106563666616</v>
+        <v>0.4915942421818189</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4915942421818189</v>
+        <v>0.5050961264345479</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5050961264345479</v>
+        <v>0.4430099781648748</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4430099781648748</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.496145303142596</v>
-      </c>
-      <c r="G12" t="n">
         <v>0.4726067888223595</v>
       </c>
     </row>
@@ -742,21 +666,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5956429695349754</v>
+        <v>0.8480678866452713</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8480678866452713</v>
+        <v>0.5785778133130111</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5785778133130111</v>
+        <v>0.8487958540737754</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8487958540737754</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5977994811228277</v>
-      </c>
-      <c r="G13" t="n">
         <v>0.8252527008912389</v>
       </c>
     </row>
@@ -767,21 +685,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8274111262282264</v>
+        <v>0.8079739363455811</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8079739363455811</v>
+        <v>0.8305685547516222</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8305685547516222</v>
+        <v>0.8098993261981159</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8098993261981159</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8250577310582088</v>
-      </c>
-      <c r="G14" t="n">
         <v>0.8073468762530275</v>
       </c>
     </row>
@@ -792,21 +704,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7992725493763905</v>
+        <v>0.8852206002728575</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8852206002728575</v>
+        <v>0.7720815646708248</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7720815646708248</v>
+        <v>0.8679345985385818</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8679345985385818</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.8218945121736206</v>
-      </c>
-      <c r="G15" t="n">
         <v>0.9203620496402012</v>
       </c>
     </row>
@@ -817,21 +723,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8956915770703451</v>
+        <v>0.9742563955453398</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9742563955453398</v>
+        <v>0.960656390362355</v>
       </c>
       <c r="D16" t="n">
-        <v>0.960656390362355</v>
+        <v>0.9842103026920026</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9842103026920026</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.8869264658153341</v>
-      </c>
-      <c r="G16" t="n">
         <v>0.9707690852790656</v>
       </c>
     </row>
